--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week06_05Oct.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week06_05Oct.xlsx
@@ -1125,7 +1125,7 @@
     <row r="8" ht="45.75" customHeight="1" s="46">
       <c r="A8" s="54" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: BHM continues — Grow PSHE W6's stereotype-smash lands squarely in it.  World Mental Health Day Sat 10 Oct — observe Fri 9; ⚠ handle with care (§8.4: advance flag, opt-out, known-adult check-in) — assembly-led, classroom framing kept light.  Hate Crime Awareness Week may fall this week (tbc).  EVIDENCE: assembly print + EFL: PfA/citizenship; care protocol logged → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: BHM continues — Grow PSHE W6's stereotype-smash lands squarely in it.  World Mental Health Day Sat 10 Oct — observe Fri 9; ⚠ handle with care (§8.4: advance flag, opt-out, known-adult check-in) — assembly-led, classroom framing kept light.  Hate Crime Awareness Week may fall this week (tbc).  EVIDENCE: assembly print + evidence platform: PfA/citizenship; care protocol logged → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="55" t="n"/>
@@ -1336,7 +1336,7 @@
 Targeted questioning to develop reasoning and decision-making skills.
 Ongoing assessment through discussion, observation and problem-solving activities.
 Positive feedback and opportunities for collaborative learning and peer support.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
         </is>
       </c>
       <c r="J11" s="63" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="I13" s="63" t="inlineStr">
         <is>
           <t>TA models a respectful disagreement first; teacher keeps the barometer moving and affirms every position honestly held; the posters/videos are the evidence.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
         </is>
       </c>
       <c r="J13" s="63" t="inlineStr">
